--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-researchsubject.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-researchsubject.xlsx
@@ -450,7 +450,7 @@
     <t>ResearchSubject.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -488,7 +488,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -546,7 +546,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -715,7 +715,7 @@
     <t>ResearchSubject.study</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ResearchStudy)
+    <t xml:space="preserve">Reference(ResearchStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -731,7 +731,7 @@
     <t>ResearchSubject.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -765,7 +765,7 @@
     <t>ResearchSubject.consent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Consent)
+    <t xml:space="preserve">Reference(Consent|4.0.1)
 </t>
   </si>
   <si>
@@ -1105,7 +1105,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="24.5625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="29.08984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
